--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="525">
   <si>
     <t>Filename</t>
   </si>
@@ -826,22 +826,25 @@
     <t>0,1,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0.9683,0.0025,0.0086,0.0019</t>
   </si>
   <si>
-    <t>0.0032,0.0068,0.0005,0.9990</t>
-  </si>
-  <si>
-    <t>0.9815,0.0019,0.0005,0.0055</t>
-  </si>
-  <si>
-    <t>0.0979,0.0016,0.0034,0.9507</t>
+    <t>0.0032,0.0069,0.0005,0.9990</t>
+  </si>
+  <si>
+    <t>0.9815,0.0019,0.0006,0.0054</t>
+  </si>
+  <si>
+    <t>0.0979,0.0016,0.0034,0.9508</t>
   </si>
   <si>
     <t>0.9950,0.0017,0.0012,0.0003</t>
   </si>
   <si>
-    <t>0.9918,0.0067,0.0007,0.0003</t>
+    <t>0.9918,0.0068,0.0007,0.0003</t>
   </si>
   <si>
     <t>0.9947,0.0015,0.0012,0.0001</t>
@@ -850,31 +853,31 @@
     <t>0.9941,0.0016,0.0013,0.0000</t>
   </si>
   <si>
-    <t>0.9869,0.0125,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9924,0.0053,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9957,0.0010,0.0008,0.0000</t>
+    <t>0.9868,0.0126,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9924,0.0054,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0011,0.0008,0.0000</t>
   </si>
   <si>
     <t>0.9956,0.0016,0.0010,0.0002</t>
   </si>
   <si>
-    <t>0.8490,0.0082,0.1240,0.0019</t>
-  </si>
-  <si>
-    <t>0.0172,0.0169,0.9734,0.0009</t>
-  </si>
-  <si>
-    <t>0.2730,0.0005,0.8551,0.0001</t>
-  </si>
-  <si>
-    <t>0.0439,0.0119,0.9527,0.0010</t>
-  </si>
-  <si>
-    <t>0.7786,0.0006,0.2725,0.0002</t>
+    <t>0.8491,0.0082,0.1238,0.0019</t>
+  </si>
+  <si>
+    <t>0.0171,0.0170,0.9735,0.0009</t>
+  </si>
+  <si>
+    <t>0.2723,0.0005,0.8555,0.0001</t>
+  </si>
+  <si>
+    <t>0.0437,0.0120,0.9527,0.0010</t>
+  </si>
+  <si>
+    <t>0.7785,0.0006,0.2724,0.0002</t>
   </si>
   <si>
     <t>0.0015,0.9982,0.0136,0.0007</t>
@@ -883,7 +886,7 @@
     <t>0.0023,0.9972,0.0052,0.0011</t>
   </si>
   <si>
-    <t>0.0297,0.9950,0.0071,0.0000</t>
+    <t>0.0296,0.9950,0.0071,0.0000</t>
   </si>
   <si>
     <t>0.0026,0.9955,0.0068,0.0019</t>
@@ -892,73 +895,73 @@
     <t>0.0007,0.9995,0.0119,0.0000</t>
   </si>
   <si>
-    <t>0.4235,0.0026,0.6719,0.0022</t>
-  </si>
-  <si>
-    <t>0.1194,0.0111,0.8928,0.0020</t>
-  </si>
-  <si>
-    <t>0.0201,0.0004,0.9906,0.0000</t>
+    <t>0.4227,0.0026,0.6726,0.0022</t>
+  </si>
+  <si>
+    <t>0.1194,0.0112,0.8927,0.0020</t>
+  </si>
+  <si>
+    <t>0.0200,0.0004,0.9906,0.0000</t>
   </si>
   <si>
     <t>0.0200,0.0030,0.9845,0.0003</t>
   </si>
   <si>
-    <t>0.0308,0.0016,0.9819,0.0003</t>
-  </si>
-  <si>
-    <t>0.0653,0.0012,0.9614,0.0003</t>
+    <t>0.0308,0.0016,0.9820,0.0003</t>
+  </si>
+  <si>
+    <t>0.0651,0.0012,0.9615,0.0003</t>
   </si>
   <si>
     <t>0.0128,0.0010,0.9916,0.0003</t>
   </si>
   <si>
-    <t>0.7212,0.1568,0.0511,0.0013</t>
-  </si>
-  <si>
-    <t>0.7971,0.3383,0.0114,0.0022</t>
+    <t>0.7198,0.1584,0.0510,0.0013</t>
+  </si>
+  <si>
+    <t>0.7964,0.3399,0.0114,0.0022</t>
   </si>
   <si>
     <t>0.0033,0.0005,0.9976,0.0004</t>
   </si>
   <si>
-    <t>0.0127,0.3335,0.8259,0.0016</t>
-  </si>
-  <si>
-    <t>0.9299,0.0043,0.0432,0.0008</t>
-  </si>
-  <si>
-    <t>0.7876,0.0140,0.1481,0.0012</t>
-  </si>
-  <si>
-    <t>0.3787,0.7338,0.0231,0.0007</t>
-  </si>
-  <si>
-    <t>0.0055,0.9759,0.5202,0.0016</t>
-  </si>
-  <si>
-    <t>0.0007,0.7675,0.9532,0.0004</t>
+    <t>0.0127,0.3347,0.8257,0.0016</t>
+  </si>
+  <si>
+    <t>0.9299,0.0043,0.0431,0.0008</t>
+  </si>
+  <si>
+    <t>0.7877,0.0142,0.1479,0.0012</t>
+  </si>
+  <si>
+    <t>0.3768,0.7358,0.0231,0.0007</t>
+  </si>
+  <si>
+    <t>0.0055,0.9759,0.5198,0.0016</t>
+  </si>
+  <si>
+    <t>0.0007,0.7681,0.9531,0.0004</t>
   </si>
   <si>
     <t>0.0009,0.0024,0.9981,0.0010</t>
   </si>
   <si>
-    <t>0.0086,0.0825,0.9700,0.0013</t>
-  </si>
-  <si>
-    <t>0.1180,0.0015,0.9037,0.0034</t>
-  </si>
-  <si>
-    <t>0.0005,0.7533,0.9388,0.0011</t>
+    <t>0.0085,0.0827,0.9701,0.0013</t>
+  </si>
+  <si>
+    <t>0.1182,0.0016,0.9035,0.0034</t>
+  </si>
+  <si>
+    <t>0.0005,0.7539,0.9388,0.0011</t>
   </si>
   <si>
     <t>0.0009,0.9932,0.0075,0.0030</t>
   </si>
   <si>
-    <t>0.0022,0.0346,0.9913,0.0019</t>
-  </si>
-  <si>
-    <t>0.0003,0.8497,0.0010,0.9655</t>
+    <t>0.0022,0.0347,0.9913,0.0019</t>
+  </si>
+  <si>
+    <t>0.0003,0.8508,0.0010,0.9653</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
@@ -973,10 +976,10 @@
     <t>0.0002,0.0090,0.9972,0.0014</t>
   </si>
   <si>
-    <t>0.0007,0.1462,0.9922,0.0014</t>
-  </si>
-  <si>
-    <t>0.0067,0.0045,0.9897,0.0010</t>
+    <t>0.0007,0.1465,0.9923,0.0014</t>
+  </si>
+  <si>
+    <t>0.0067,0.0045,0.9898,0.0010</t>
   </si>
   <si>
     <t>0.0222,0.0002,0.9917,0.0001</t>
@@ -985,7 +988,7 @@
     <t>0.0086,0.0015,0.9930,0.0001</t>
   </si>
   <si>
-    <t>0.0280,0.0203,0.9571,0.0013</t>
+    <t>0.0280,0.0203,0.9572,0.0013</t>
   </si>
   <si>
     <t>0.9830,0.0061,0.0053,0.0001</t>
@@ -997,28 +1000,28 @@
     <t>0.9738,0.0129,0.0093,0.0037</t>
   </si>
   <si>
-    <t>0.3468,0.0013,0.7269,0.0003</t>
+    <t>0.3463,0.0013,0.7270,0.0003</t>
   </si>
   <si>
     <t>0.9892,0.0003,0.0064,0.0001</t>
   </si>
   <si>
-    <t>0.9924,0.0016,0.0029,0.0002</t>
+    <t>0.9924,0.0016,0.0030,0.0002</t>
   </si>
   <si>
     <t>0.9951,0.0006,0.0017,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.9991,0.9009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1711,0.9986,0.0002</t>
+    <t>0.0000,0.9991,0.9008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1715,0.9986,0.0002</t>
   </si>
   <si>
     <t>0.0014,0.0163,0.9935,0.0014</t>
   </si>
   <si>
-    <t>0.0002,0.9840,0.8910,0.0004</t>
+    <t>0.0002,0.9840,0.8909,0.0004</t>
   </si>
   <si>
     <t>0.0002,0.0003,0.9996,0.0001</t>
@@ -1033,25 +1036,25 @@
     <t>0.9845,0.0002,0.0146,0.0000</t>
   </si>
   <si>
-    <t>0.1120,0.0235,0.8773,0.0021</t>
+    <t>0.1117,0.0236,0.8774,0.0021</t>
   </si>
   <si>
     <t>0.0133,0.0031,0.9904,0.0003</t>
   </si>
   <si>
-    <t>0.0003,0.8737,0.9817,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9305,0.9845,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.3235,0.0000</t>
+    <t>0.0003,0.8741,0.9817,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9306,0.9845,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.3229,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.9834,0.9729,0.0001</t>
   </si>
   <si>
-    <t>0.0009,0.0039,0.0008,0.9998</t>
+    <t>0.0009,0.0039,0.0008,0.9997</t>
   </si>
   <si>
     <t>0.0008,0.0009,0.0001,0.9999</t>
@@ -1069,31 +1072,31 @@
     <t>0.0004,0.0026,0.0018,0.9998</t>
   </si>
   <si>
-    <t>0.0000,0.9977,0.9128,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9264,0.9944,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9497,0.8123,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.5414,0.9938,0.0004</t>
+    <t>0.0000,0.9977,0.9126,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9266,0.9944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9499,0.8125,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.5418,0.9938,0.0004</t>
   </si>
   <si>
     <t>0.0000,0.9924,0.9909,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9919,0.7481,0.0001</t>
+    <t>0.0002,0.9920,0.7482,0.0001</t>
   </si>
   <si>
     <t>0.9946,0.0050,0.0004,0.0002</t>
   </si>
   <si>
-    <t>0.9852,0.0116,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9797,0.0282,0.0006,0.0002</t>
+    <t>0.9852,0.0117,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9796,0.0284,0.0006,0.0002</t>
   </si>
   <si>
     <t>0.9946,0.0033,0.0007,0.0002</t>
@@ -1114,7 +1117,7 @@
     <t>0.9958,0.0005,0.0009,0.0002</t>
   </si>
   <si>
-    <t>0.9952,0.0025,0.0008,0.0002</t>
+    <t>0.9952,0.0026,0.0008,0.0002</t>
   </si>
   <si>
     <t>0.9973,0.0010,0.0003,0.0001</t>
@@ -1132,19 +1135,19 @@
     <t>0.9963,0.0014,0.0005,0.0004</t>
   </si>
   <si>
-    <t>0.9934,0.0014,0.0017,0.0002</t>
+    <t>0.9933,0.0014,0.0017,0.0002</t>
   </si>
   <si>
     <t>0.0025,0.0002,0.9987,0.0000</t>
   </si>
   <si>
-    <t>0.0161,0.0014,0.9887,0.0002</t>
-  </si>
-  <si>
-    <t>0.9674,0.0001,0.0420,0.0000</t>
-  </si>
-  <si>
-    <t>0.0272,0.0012,0.9825,0.0001</t>
+    <t>0.0161,0.0014,0.9888,0.0002</t>
+  </si>
+  <si>
+    <t>0.9673,0.0001,0.0421,0.0000</t>
+  </si>
+  <si>
+    <t>0.0271,0.0012,0.9825,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0003,0.0001</t>
@@ -1153,10 +1156,10 @@
     <t>0.0001,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.2534,0.8721,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.0371,0.9742,0.0136,0.0019</t>
+    <t>0.2526,0.8729,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.0369,0.9744,0.0136,0.0019</t>
   </si>
   <si>
     <t>0.0003,0.9996,0.0004,0.0001</t>
@@ -1165,22 +1168,22 @@
     <t>0.0000,1.0000,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.6405,0.4923,0.0179,0.0006</t>
-  </si>
-  <si>
-    <t>0.1006,0.0201,0.8934,0.0037</t>
-  </si>
-  <si>
-    <t>0.0261,0.0093,0.9718,0.0010</t>
-  </si>
-  <si>
-    <t>0.3075,0.0136,0.6862,0.0030</t>
-  </si>
-  <si>
-    <t>0.1113,0.0176,0.8965,0.0037</t>
-  </si>
-  <si>
-    <t>0.0002,0.6021,0.5404,0.2143</t>
+    <t>0.6391,0.4944,0.0179,0.0006</t>
+  </si>
+  <si>
+    <t>0.1007,0.0203,0.8931,0.0037</t>
+  </si>
+  <si>
+    <t>0.0260,0.0093,0.9719,0.0010</t>
+  </si>
+  <si>
+    <t>0.3075,0.0136,0.6859,0.0030</t>
+  </si>
+  <si>
+    <t>0.1112,0.0177,0.8964,0.0037</t>
+  </si>
+  <si>
+    <t>0.0002,0.6032,0.5405,0.2136</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0008,0.0001</t>
@@ -1189,70 +1192,70 @@
     <t>0.0000,0.9999,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9991,0.0007,0.0072</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0614,0.0011</t>
-  </si>
-  <si>
-    <t>0.0028,0.9961,0.0569,0.0002</t>
-  </si>
-  <si>
-    <t>0.4567,0.5441,0.0600,0.0021</t>
-  </si>
-  <si>
-    <t>0.1923,0.8355,0.0238,0.0041</t>
+    <t>0.0001,0.9991,0.0007,0.0071</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0612,0.0011</t>
+  </si>
+  <si>
+    <t>0.0028,0.9962,0.0569,0.0002</t>
+  </si>
+  <si>
+    <t>0.4551,0.5466,0.0600,0.0021</t>
+  </si>
+  <si>
+    <t>0.1916,0.8362,0.0237,0.0041</t>
   </si>
   <si>
     <t>0.9971,0.0003,0.0006,0.0003</t>
   </si>
   <si>
-    <t>0.9819,0.0107,0.0011,0.0018</t>
-  </si>
-  <si>
-    <t>0.9910,0.0032,0.0012,0.0008</t>
+    <t>0.9818,0.0108,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.9909,0.0033,0.0012,0.0008</t>
   </si>
   <si>
     <t>0.9892,0.0014,0.0042,0.0004</t>
   </si>
   <si>
-    <t>0.9986,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9867,0.0022,0.0041,0.0010</t>
-  </si>
-  <si>
-    <t>0.9908,0.0020,0.0020,0.0003</t>
+    <t>0.9986,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9867,0.0023,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.9907,0.0020,0.0020,0.0003</t>
   </si>
   <si>
     <t>0.9913,0.0008,0.0030,0.0002</t>
   </si>
   <si>
-    <t>0.0002,0.9710,0.9659,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.4382,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0194,0.9985,0.0003</t>
+    <t>0.0002,0.9711,0.9659,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.4389,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0195,0.9985,0.0003</t>
   </si>
   <si>
     <t>0.0039,0.0066,0.9954,0.0001</t>
   </si>
   <si>
-    <t>0.9492,0.0016,0.0371,0.0003</t>
-  </si>
-  <si>
-    <t>0.3385,0.4561,0.0662,0.0053</t>
-  </si>
-  <si>
-    <t>0.1443,0.0004,0.9229,0.0005</t>
-  </si>
-  <si>
-    <t>0.8053,0.0039,0.1891,0.0015</t>
-  </si>
-  <si>
-    <t>0.0045,0.0005,0.0014,0.9994</t>
+    <t>0.9492,0.0016,0.0370,0.0003</t>
+  </si>
+  <si>
+    <t>0.3370,0.4583,0.0658,0.0052</t>
+  </si>
+  <si>
+    <t>0.1439,0.0004,0.9231,0.0005</t>
+  </si>
+  <si>
+    <t>0.8052,0.0039,0.1891,0.0015</t>
+  </si>
+  <si>
+    <t>0.0045,0.0005,0.0014,0.9993</t>
   </si>
   <si>
     <t>0.0000,0.0010,0.0009,1.0000</t>
@@ -1270,64 +1273,64 @@
     <t>0.9815,0.0008,0.0100,0.0003</t>
   </si>
   <si>
-    <t>0.0098,0.9868,0.0156,0.0064</t>
+    <t>0.0098,0.9869,0.0155,0.0064</t>
   </si>
   <si>
     <t>0.9945,0.0005,0.0020,0.0001</t>
   </si>
   <si>
-    <t>0.0159,0.9851,0.0128,0.0011</t>
+    <t>0.0158,0.9852,0.0128,0.0011</t>
   </si>
   <si>
     <t>0.9932,0.0010,0.0010,0.0009</t>
   </si>
   <si>
-    <t>0.8106,0.0000,0.4552,0.0000</t>
-  </si>
-  <si>
-    <t>0.7292,0.0000,0.4926,0.0000</t>
+    <t>0.8110,0.0000,0.4545,0.0000</t>
+  </si>
+  <si>
+    <t>0.7296,0.0000,0.4919,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9443,0.0004,0.0344,0.0004</t>
-  </si>
-  <si>
-    <t>0.9706,0.0182,0.0074,0.0008</t>
-  </si>
-  <si>
-    <t>0.5690,0.2752,0.0374,0.0023</t>
+    <t>0.9444,0.0004,0.0343,0.0004</t>
+  </si>
+  <si>
+    <t>0.9704,0.0184,0.0075,0.0008</t>
+  </si>
+  <si>
+    <t>0.5684,0.2763,0.0373,0.0023</t>
   </si>
   <si>
     <t>0.9905,0.0008,0.0039,0.0001</t>
   </si>
   <si>
-    <t>0.9398,0.0201,0.0165,0.0010</t>
-  </si>
-  <si>
-    <t>0.1723,0.7697,0.0659,0.0221</t>
-  </si>
-  <si>
-    <t>0.9141,0.0195,0.0331,0.0007</t>
-  </si>
-  <si>
-    <t>0.9529,0.0014,0.0369,0.0003</t>
+    <t>0.9397,0.0202,0.0165,0.0010</t>
+  </si>
+  <si>
+    <t>0.1716,0.7710,0.0657,0.0220</t>
+  </si>
+  <si>
+    <t>0.9140,0.0196,0.0330,0.0007</t>
+  </si>
+  <si>
+    <t>0.9528,0.0014,0.0369,0.0003</t>
   </si>
   <si>
     <t>0.9946,0.0023,0.0010,0.0002</t>
   </si>
   <si>
-    <t>0.9961,0.0022,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9917,0.0014,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9886,0.0012,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.9945,0.0021,0.0010,0.0001</t>
+    <t>0.9961,0.0022,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9917,0.0015,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.9886,0.0012,0.0040,0.0002</t>
+  </si>
+  <si>
+    <t>0.9945,0.0022,0.0010,0.0001</t>
   </si>
   <si>
     <t>0.9919,0.0034,0.0014,0.0004</t>
@@ -1339,46 +1342,46 @@
     <t>0.9917,0.0014,0.0019,0.0001</t>
   </si>
   <si>
-    <t>0.6901,0.3641,0.0029,0.0016</t>
-  </si>
-  <si>
-    <t>0.2452,0.7641,0.0286,0.0123</t>
-  </si>
-  <si>
-    <t>0.8773,0.1130,0.0054,0.0009</t>
-  </si>
-  <si>
-    <t>0.9353,0.0331,0.0231,0.0022</t>
+    <t>0.6895,0.3654,0.0029,0.0016</t>
+  </si>
+  <si>
+    <t>0.2444,0.7652,0.0286,0.0122</t>
+  </si>
+  <si>
+    <t>0.8766,0.1140,0.0054,0.0009</t>
+  </si>
+  <si>
+    <t>0.9350,0.0333,0.0231,0.0022</t>
   </si>
   <si>
     <t>0.9869,0.0061,0.0030,0.0001</t>
   </si>
   <si>
-    <t>0.9628,0.0300,0.0052,0.0006</t>
+    <t>0.9626,0.0303,0.0052,0.0006</t>
   </si>
   <si>
     <t>0.9873,0.0016,0.0056,0.0001</t>
   </si>
   <si>
-    <t>0.9466,0.0240,0.0144,0.0012</t>
-  </si>
-  <si>
-    <t>0.0118,0.0026,0.9925,0.0001</t>
-  </si>
-  <si>
-    <t>0.9451,0.0356,0.0079,0.0003</t>
+    <t>0.9464,0.0242,0.0144,0.0012</t>
+  </si>
+  <si>
+    <t>0.0117,0.0026,0.9925,0.0001</t>
+  </si>
+  <si>
+    <t>0.9448,0.0359,0.0079,0.0003</t>
   </si>
   <si>
     <t>0.0004,0.0007,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0651,0.9925,0.0047</t>
-  </si>
-  <si>
-    <t>0.0130,0.0021,0.9900,0.0006</t>
-  </si>
-  <si>
-    <t>0.0020,0.3684,0.9724,0.0007</t>
+    <t>0.0002,0.0654,0.9925,0.0047</t>
+  </si>
+  <si>
+    <t>0.0129,0.0021,0.9901,0.0006</t>
+  </si>
+  <si>
+    <t>0.0020,0.3692,0.9724,0.0007</t>
   </si>
   <si>
     <t>0.0016,0.0034,0.9978,0.0001</t>
@@ -1387,109 +1390,109 @@
     <t>0.0015,0.0002,0.9992,0.0000</t>
   </si>
   <si>
-    <t>0.0124,0.0015,0.9913,0.0001</t>
-  </si>
-  <si>
-    <t>0.0901,0.0056,0.9275,0.0008</t>
-  </si>
-  <si>
-    <t>0.1250,0.0022,0.9173,0.0005</t>
-  </si>
-  <si>
-    <t>0.7405,0.0445,0.1544,0.0028</t>
-  </si>
-  <si>
-    <t>0.0571,0.0316,0.8958,0.0013</t>
-  </si>
-  <si>
-    <t>0.0139,0.0709,0.9398,0.0003</t>
-  </si>
-  <si>
-    <t>0.0643,0.0044,0.9486,0.0008</t>
-  </si>
-  <si>
-    <t>0.2327,0.0073,0.7960,0.0036</t>
-  </si>
-  <si>
-    <t>0.5781,0.0470,0.2960,0.0017</t>
-  </si>
-  <si>
-    <t>0.1327,0.9485,0.0079,0.0002</t>
+    <t>0.0123,0.0015,0.9913,0.0001</t>
+  </si>
+  <si>
+    <t>0.0899,0.0056,0.9276,0.0008</t>
+  </si>
+  <si>
+    <t>0.1246,0.0022,0.9175,0.0005</t>
+  </si>
+  <si>
+    <t>0.7403,0.0447,0.1543,0.0028</t>
+  </si>
+  <si>
+    <t>0.0569,0.0316,0.8959,0.0013</t>
+  </si>
+  <si>
+    <t>0.0139,0.0712,0.9397,0.0003</t>
+  </si>
+  <si>
+    <t>0.0642,0.0044,0.9486,0.0008</t>
+  </si>
+  <si>
+    <t>0.2323,0.0073,0.7963,0.0036</t>
+  </si>
+  <si>
+    <t>0.5776,0.0473,0.2959,0.0017</t>
+  </si>
+  <si>
+    <t>0.1323,0.9487,0.0079,0.0002</t>
   </si>
   <si>
     <t>0.0023,0.9979,0.0044,0.0004</t>
   </si>
   <si>
-    <t>0.0581,0.9581,0.0037,0.0013</t>
-  </si>
-  <si>
-    <t>0.9777,0.0100,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.3787,0.7207,0.0061,0.0006</t>
-  </si>
-  <si>
-    <t>0.2279,0.7042,0.0200,0.0006</t>
-  </si>
-  <si>
-    <t>0.9543,0.0073,0.0146,0.0002</t>
-  </si>
-  <si>
-    <t>0.3367,0.0454,0.6099,0.0143</t>
-  </si>
-  <si>
-    <t>0.1079,0.0044,0.9113,0.0037</t>
-  </si>
-  <si>
-    <t>0.5524,0.0166,0.3650,0.0034</t>
-  </si>
-  <si>
-    <t>0.0109,0.0020,0.9908,0.0004</t>
-  </si>
-  <si>
-    <t>0.1037,0.0038,0.9014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0311,0.0390,0.9298,0.0002</t>
+    <t>0.0576,0.9585,0.0037,0.0013</t>
+  </si>
+  <si>
+    <t>0.9776,0.0101,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.3763,0.7233,0.0061,0.0006</t>
+  </si>
+  <si>
+    <t>0.2274,0.7052,0.0199,0.0006</t>
+  </si>
+  <si>
+    <t>0.9543,0.0074,0.0146,0.0002</t>
+  </si>
+  <si>
+    <t>0.3365,0.0457,0.6097,0.0143</t>
+  </si>
+  <si>
+    <t>0.1078,0.0044,0.9114,0.0037</t>
+  </si>
+  <si>
+    <t>0.5526,0.0168,0.3641,0.0034</t>
+  </si>
+  <si>
+    <t>0.0108,0.0020,0.9908,0.0004</t>
+  </si>
+  <si>
+    <t>0.1040,0.0038,0.9010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0311,0.0393,0.9295,0.0002</t>
   </si>
   <si>
     <t>0.0024,0.0104,0.9949,0.0008</t>
   </si>
   <si>
-    <t>0.0045,0.0068,0.9927,0.0002</t>
+    <t>0.0045,0.0069,0.9927,0.0002</t>
   </si>
   <si>
     <t>0.9955,0.0005,0.0011,0.0001</t>
   </si>
   <si>
-    <t>0.9834,0.0094,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.9808,0.0091,0.0027,0.0025</t>
+    <t>0.9834,0.0095,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.9807,0.0092,0.0027,0.0025</t>
   </si>
   <si>
     <t>0.9906,0.0068,0.0003,0.0003</t>
   </si>
   <si>
-    <t>0.9630,0.0291,0.0053,0.0021</t>
-  </si>
-  <si>
-    <t>0.9702,0.0287,0.0034,0.0012</t>
-  </si>
-  <si>
-    <t>0.9920,0.0061,0.0011,0.0004</t>
+    <t>0.9628,0.0295,0.0053,0.0021</t>
+  </si>
+  <si>
+    <t>0.9701,0.0291,0.0034,0.0012</t>
+  </si>
+  <si>
+    <t>0.9920,0.0062,0.0011,0.0004</t>
   </si>
   <si>
     <t>0.9946,0.0010,0.0013,0.0001</t>
   </si>
   <si>
-    <t>0.0085,0.0030,0.9932,0.0005</t>
-  </si>
-  <si>
-    <t>0.0637,0.0250,0.9064,0.0008</t>
-  </si>
-  <si>
-    <t>0.5019,0.0053,0.4862,0.0127</t>
+    <t>0.0084,0.0031,0.9932,0.0005</t>
+  </si>
+  <si>
+    <t>0.0636,0.0252,0.9062,0.0008</t>
+  </si>
+  <si>
+    <t>0.5011,0.0054,0.4870,0.0127</t>
   </si>
   <si>
     <t>0.0018,0.0007,0.9987,0.0001</t>
@@ -1498,7 +1501,7 @@
     <t>0.0003,0.0022,0.9992,0.0002</t>
   </si>
   <si>
-    <t>0.0048,0.0252,0.9857,0.0008</t>
+    <t>0.0048,0.0253,0.9856,0.0008</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.9999,0.0000</t>
@@ -1510,10 +1513,10 @@
     <t>0.0039,0.0085,0.9938,0.0005</t>
   </si>
   <si>
-    <t>0.0478,0.0136,0.9416,0.0021</t>
-  </si>
-  <si>
-    <t>0.7686,0.0019,0.2640,0.0011</t>
+    <t>0.0478,0.0136,0.9417,0.0021</t>
+  </si>
+  <si>
+    <t>0.7685,0.0019,0.2641,0.0011</t>
   </si>
   <si>
     <t>0.4999,0.0015,0.5082,0.0063</t>
@@ -1525,19 +1528,19 @@
     <t>0.9953,0.0018,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9897,0.0101,0.0006,0.0004</t>
+    <t>0.9896,0.0102,0.0006,0.0004</t>
   </si>
   <si>
     <t>0.9947,0.0029,0.0008,0.0001</t>
   </si>
   <si>
-    <t>0.9508,0.0389,0.0047,0.0008</t>
+    <t>0.9505,0.0394,0.0047,0.0008</t>
   </si>
   <si>
     <t>0.9940,0.0012,0.0013,0.0001</t>
   </si>
   <si>
-    <t>0.9881,0.0100,0.0016,0.0004</t>
+    <t>0.9880,0.0101,0.0015,0.0004</t>
   </si>
   <si>
     <t>0.9956,0.0019,0.0006,0.0002</t>
@@ -1546,7 +1549,7 @@
     <t>0.9870,0.0022,0.0036,0.0013</t>
   </si>
   <si>
-    <t>0.0086,0.0289,0.9797,0.0006</t>
+    <t>0.0086,0.0290,0.9797,0.0006</t>
   </si>
   <si>
     <t>0.0010,0.0038,0.9988,0.0000</t>
@@ -1555,16 +1558,16 @@
     <t>0.0024,0.0024,0.9975,0.0000</t>
   </si>
   <si>
-    <t>0.0114,0.0599,0.9502,0.0007</t>
-  </si>
-  <si>
-    <t>0.0107,0.0019,0.9919,0.0001</t>
-  </si>
-  <si>
-    <t>0.7447,0.0566,0.1144,0.0064</t>
-  </si>
-  <si>
-    <t>0.0710,0.0233,0.9055,0.0049</t>
+    <t>0.0113,0.0601,0.9501,0.0007</t>
+  </si>
+  <si>
+    <t>0.0106,0.0019,0.9920,0.0001</t>
+  </si>
+  <si>
+    <t>0.7453,0.0572,0.1138,0.0064</t>
+  </si>
+  <si>
+    <t>0.0710,0.0234,0.9053,0.0049</t>
   </si>
   <si>
     <t>0.0013,0.0005,0.9983,0.0008</t>
@@ -1573,10 +1576,10 @@
     <t>0.9692,0.0007,0.0043,0.0044</t>
   </si>
   <si>
-    <t>0.0007,0.0038,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0085,0.0002,0.0009,0.9992</t>
+    <t>0.0007,0.0039,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0086,0.0002,0.0009,0.9992</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.0038,0.9999</t>
@@ -1585,7 +1588,7 @@
     <t>0.0002,0.0002,0.0011,0.9999</t>
   </si>
   <si>
-    <t>0.6811,0.0123,0.0168,0.2371</t>
+    <t>0.6813,0.0124,0.0168,0.2364</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1974,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1988,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2002,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2016,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2030,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2044,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2058,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2072,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2086,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2100,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2114,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2128,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2142,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2153,7 +2156,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2170,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2184,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2198,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2209,7 +2212,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2223,7 +2226,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2237,7 +2240,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2251,7 +2254,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2265,7 +2268,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2282,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2293,7 +2296,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2307,7 +2310,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2321,7 +2324,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2335,7 +2338,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2349,7 +2352,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2363,7 +2366,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2380,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2394,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2405,7 +2408,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2419,7 +2422,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2436,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2450,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2461,7 +2464,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2475,7 +2478,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2489,7 +2492,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2503,7 +2506,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2517,7 +2520,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2531,7 +2534,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2545,7 +2548,7 @@
         <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2559,7 +2562,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2573,7 +2576,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2590,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2601,7 +2604,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2615,7 +2618,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2629,7 +2632,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2643,7 +2646,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2657,7 +2660,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2671,7 +2674,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2685,7 +2688,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2699,7 +2702,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2713,7 +2716,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2730,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2744,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2758,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2769,7 +2772,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2786,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2800,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2814,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2825,7 +2828,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2839,7 +2842,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2853,7 +2856,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2867,7 +2870,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2881,7 +2884,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2895,7 +2898,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2909,7 +2912,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2926,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2937,7 +2940,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2951,7 +2954,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2965,7 +2968,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2979,7 +2982,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2993,7 +2996,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3007,7 +3010,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3024,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3038,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3052,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3066,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3080,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3094,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3105,7 +3108,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3119,7 +3122,7 @@
         <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3133,7 +3136,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3147,7 +3150,7 @@
         <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3161,7 +3164,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3175,7 +3178,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3192,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3206,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3220,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3234,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3248,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3262,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3276,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3290,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3304,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3318,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3332,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3346,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3360,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3374,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3388,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3402,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3413,7 +3416,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3427,7 +3430,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3444,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3455,7 +3458,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3469,7 +3472,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3483,7 +3486,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,7 +3500,7 @@
         <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3511,7 +3514,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3525,7 +3528,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3539,7 +3542,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3556,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3570,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3584,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3598,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3612,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3623,7 +3626,7 @@
         <v>268</v>
       </c>
       <c r="D120" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3637,7 +3640,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3651,7 +3654,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3665,7 +3668,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3679,7 +3682,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3693,7 +3696,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3707,7 +3710,7 @@
         <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3721,7 +3724,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3738,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3752,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3766,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3780,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3794,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3808,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3822,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3836,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3847,7 +3850,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3861,7 +3864,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3875,7 +3878,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3889,7 +3892,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3906,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,10 +3917,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D141" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3934,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3948,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3962,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3976,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3990,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4004,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4015,7 +4018,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4032,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4043,7 +4046,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4060,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,7 +4074,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4088,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4099,7 +4102,7 @@
         <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4113,7 +4116,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4127,7 +4130,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4144,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4158,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4172,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4186,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4200,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4211,7 +4214,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4228,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4242,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4256,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4270,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4284,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4298,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4312,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4326,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4340,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4354,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,7 +4368,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4382,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4396,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4410,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4424,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4438,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4452,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4466,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4477,7 +4480,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4494,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4505,7 +4508,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4519,7 +4522,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4533,7 +4536,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4547,7 +4550,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4561,7 +4564,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4575,7 +4578,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4589,7 +4592,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4603,7 +4606,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4620,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4634,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4648,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4659,7 +4662,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4676,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4690,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4704,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,7 +4718,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4729,7 +4732,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4743,7 +4746,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4760,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4774,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4788,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4802,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4816,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4830,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,7 +4844,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4855,7 +4858,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4869,7 +4872,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4883,7 +4886,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4897,7 +4900,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4911,7 +4914,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4928,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4942,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4956,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4970,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4984,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +4998,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5012,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5026,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5037,7 +5040,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5051,7 +5054,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5065,7 +5068,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5079,7 +5082,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5093,7 +5096,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5107,7 +5110,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5121,7 +5124,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5135,7 +5138,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5149,7 +5152,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5163,7 +5166,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5177,7 +5180,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5194,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5208,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5222,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5236,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5250,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5264,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5278,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5292,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5306,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5320,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5334,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5345,7 +5348,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5359,7 +5362,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5373,7 +5376,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5387,7 +5390,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5401,7 +5404,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5418,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5429,7 +5432,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5443,7 +5446,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5460,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5474,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5488,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5502,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5516,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5530,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
